--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484704_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484704_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2023</v>
+        <v>7.2817</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4011</v>
+        <v>5.7035</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8012</v>
+        <v>1.5783</v>
       </c>
       <c r="G2" t="n">
         <v>5.9799</v>
@@ -610,13 +610,13 @@
         <v>3.4819</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4948</v>
+        <v>-0.4154</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.552</v>
+        <v>-0.2496</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0572</v>
+        <v>-0.1658</v>
       </c>
       <c r="V2" t="n">
         <v>1.9005</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0959</v>
+        <v>6.5541</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2534</v>
+        <v>5.1327</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8425</v>
+        <v>1.4214</v>
       </c>
       <c r="G3" t="n">
         <v>3.9681</v>
@@ -688,13 +688,13 @@
         <v>3.4819</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8276</v>
+        <v>-0.3694</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3031</v>
+        <v>-0.4238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4756</v>
+        <v>0.0544</v>
       </c>
       <c r="V3" t="n">
         <v>2.2224</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1026</v>
+        <v>1.7144</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.929</v>
+        <v>0.3919</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0316</v>
+        <v>1.3225</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5179</v>
+        <v>1.0455</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0147</v>
+        <v>0.6609</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5032</v>
+        <v>0.3846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5109</v>
+        <v>0.1084</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8643</v>
+        <v>0.1084</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3753</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0069</v>
+        <v>0.9371</v>
       </c>
       <c r="N4" t="n">
-        <v>0.879</v>
+        <v>0.5525</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1279</v>
+        <v>0.3846</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1633</v>
+        <v>-0.0641</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0053</v>
+        <v>0.2836</v>
       </c>
       <c r="U4" t="n">
-        <v>0.158</v>
+        <v>-0.3477</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6127</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8076</v>
+        <v>1.4712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.6843</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2234</v>
+        <v>3.1555</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0455</v>
+        <v>1.5179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6609</v>
+        <v>0.0147</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3846</v>
+        <v>1.5032</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1084</v>
+        <v>0.5109</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1084</v>
+        <v>-0.8643</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.3753</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9371</v>
+        <v>1.0069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5525</v>
+        <v>0.879</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3846</v>
+        <v>0.1279</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0291</v>
+        <v>0.5319</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4759</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4468</v>
+        <v>0.2818</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6127</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3155</v>
+        <v>-0.0276</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6729</v>
+        <v>-0.2269</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3574</v>
+        <v>0.1993</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2483</v>
+        <v>0.604</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7553</v>
+        <v>0.7964</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0037</v>
+        <v>-0.1925</v>
       </c>
       <c r="J7" t="n">
-        <v>2.225</v>
+        <v>0.8545</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4332</v>
+        <v>0.8545</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7917999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4733</v>
+        <v>-0.2505</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6778</v>
+        <v>-0.0581</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7955</v>
+        <v>-0.1925</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0532</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0423</v>
+        <v>-0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0109</v>
+        <v>-0.4664</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1763</v>
+        <v>-0.5083</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2269</v>
+        <v>1.7253</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0507</v>
+        <v>-2.2336</v>
       </c>
       <c r="G8" t="n">
-        <v>0.604</v>
+        <v>-0.2483</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7964</v>
+        <v>0.7553</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1925</v>
+        <v>-1.0037</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8545</v>
+        <v>2.225</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8545</v>
+        <v>1.4332</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2505</v>
+        <v>-2.4733</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0581</v>
+        <v>-0.6778</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1925</v>
+        <v>-1.7955</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7802</v>
+        <v>0.2294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6151</v>
+        <v>0.1348</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1778</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7934</v>
+        <v>0.9857</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9711</v>
+        <v>-1.7977</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4162</v>
@@ -1156,13 +1156,13 @@
         <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6725</v>
+        <v>-0.3068</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3972</v>
+        <v>-0.2238</v>
       </c>
       <c r="V9" t="n">
         <v>0.6439</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. LLOPIS FELIPO</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3525</v>
+        <v>-2.2103</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0316</v>
+        <v>-0.3026</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3842</v>
+        <v>-1.9077</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1406</v>
+        <v>-0.9776</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4353</v>
+        <v>-1.2082</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7053</v>
+        <v>0.2307</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0867</v>
+        <v>1.2393</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0867</v>
+        <v>-0.1458</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3851</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2273</v>
+        <v>-2.2169</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.522</v>
+        <v>-1.0624</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7053</v>
+        <v>-1.1544</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3115</v>
+        <v>0.0788</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0551</v>
+        <v>-0.382</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2564</v>
+        <v>0.4608</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.267</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5039</v>
+        <v>-2.2711</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8935</v>
+        <v>0.0456</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6105</v>
+        <v>-2.3167</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9776</v>
+        <v>-0.0228</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2082</v>
+        <v>0.266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2307</v>
+        <v>-0.2888</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2393</v>
+        <v>0.7179</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1458</v>
+        <v>0.7179</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3851</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2169</v>
+        <v>-0.7407</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0624</v>
+        <v>-0.4519</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1544</v>
+        <v>-0.2888</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3823</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2148</v>
+        <v>-0.4761</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9728</v>
+        <v>-0.1067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.758</v>
+        <v>-0.3694</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.945</v>
+        <v>-1.5889</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5339</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>V. LLOPIS FELIPO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0243</v>
+        <v>-2.3525</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4352</v>
+        <v>0.0316</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5892</v>
+        <v>-2.3842</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0228</v>
+        <v>-1.1406</v>
       </c>
       <c r="H12" t="n">
-        <v>0.266</v>
+        <v>-0.4353</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2888</v>
+        <v>-0.7053</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7179</v>
+        <v>0.0867</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7179</v>
+        <v>0.0867</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7407</v>
+        <v>-1.2273</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4519</v>
+        <v>-0.522</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2888</v>
+        <v>-0.7053</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2293</v>
+        <v>-0.3115</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5875</v>
+        <v>-0.0551</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6419</v>
+        <v>-0.2564</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8559</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2644</v>
+        <v>9.814900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>12.2273</v>
+        <v>12.7778</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.963</v>
+        <v>-2.9629</v>
       </c>
       <c r="G13" t="n">
         <v>11.2852</v>
@@ -1456,7 +1456,7 @@
         <v>-2.3974</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.177200000000001</v>
+        <v>-8.177199999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.8324</v>
@@ -1468,13 +1468,13 @@
         <v>17.4094</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2851</v>
+        <v>-1.7348</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3875</v>
+        <v>-0.8371000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.8976999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.568</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4924</v>
+        <v>3.4671</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9323</v>
+        <v>5.6054</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4399</v>
+        <v>-2.1383</v>
       </c>
       <c r="G14" t="n">
         <v>4.7019</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7826</v>
+        <v>0.1921</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0119</v>
+        <v>0.2898</v>
       </c>
       <c r="V14" t="n">
         <v>0.9554</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4137</v>
+        <v>0.0174</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2559</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.8422</v>
+        <v>0.5301</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.492</v>
+        <v>-0.0218</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.925</v>
+        <v>-0.6373</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5669</v>
+        <v>0.6156</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3471</v>
+        <v>0.6393</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1766</v>
+        <v>-0.1366</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1705</v>
+        <v>0.7759</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8391</v>
+        <v>-0.6611</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.1017</v>
+        <v>-0.5008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1603</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3717</v>
+        <v>-0.2436</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2074</v>
+        <v>-0.2356</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1643</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2701</v>
+        <v>-0.2026</v>
       </c>
       <c r="E17" t="n">
-        <v>0.105</v>
+        <v>3.4867</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1651</v>
+        <v>-3.6892</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4569</v>
+        <v>-1.492</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1142</v>
+        <v>-0.925</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6572</v>
+        <v>-0.5669</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0126</v>
+        <v>2.3471</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8302</v>
+        <v>2.1766</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8176</v>
+        <v>0.1705</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4443</v>
+        <v>-3.8391</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.284</v>
+        <v>-3.1017</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1603</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5542</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6282</v>
+        <v>0.4382</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.074</v>
+        <v>0.3173</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3219</v>
+        <v>2.5339</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9658</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>L. BARCOS PERALTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6148</v>
+        <v>-0.379</v>
       </c>
       <c r="E18" t="n">
-        <v>1.697</v>
+        <v>-1.2414</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3119</v>
+        <v>0.8625</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.471</v>
+        <v>-1.0482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9518</v>
+        <v>0.1407</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5192</v>
+        <v>-1.1889</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8064</v>
+        <v>-0.7245</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5882</v>
+        <v>0.4644</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2182</v>
+        <v>-1.1889</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2774</v>
+        <v>-0.3237</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.54</v>
+        <v>-0.3237</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>-0.5498</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4609</v>
+        <v>0.274</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4563</v>
+        <v>0.0487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0047</v>
+        <v>0.2253</v>
       </c>
       <c r="V18" t="n">
         <v>0.945</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MERENCIO FERRER</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.676</v>
+        <v>-0.7628</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9373</v>
+        <v>-0.9527</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2613</v>
+        <v>0.1899</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9242</v>
+        <v>-0.4569</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4723</v>
+        <v>-1.1142</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5481</v>
+        <v>0.6572</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1929</v>
+        <v>-0.0126</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9014</v>
+        <v>-0.8302</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7085</v>
+        <v>0.8176</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7312</v>
+        <v>-0.4443</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5709</v>
+        <v>-0.284</v>
       </c>
       <c r="O19" t="n">
         <v>-0.1603</v>
       </c>
       <c r="P19" t="n">
-        <v>0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5152</v>
+        <v>0.5213</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557</v>
+        <v>0.5705</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2595</v>
+        <v>-0.0492</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BARCOS PERALTA</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7913</v>
+        <v>-0.7692</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5299</v>
+        <v>1.2163</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7386</v>
+        <v>-1.9855</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0482</v>
+        <v>-1.471</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1407</v>
+        <v>-0.9518</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1889</v>
+        <v>-0.5192</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7245</v>
+        <v>1.8064</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4644</v>
+        <v>1.5882</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1889</v>
+        <v>0.2182</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3237</v>
+        <v>-3.2774</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3237</v>
+        <v>-2.54</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>-0.5498</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1384</v>
+        <v>0.3066</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2398</v>
+        <v>-0.0245</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1014</v>
+        <v>0.3311</v>
       </c>
       <c r="V20" t="n">
         <v>0.945</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>J. MERENCIO FERRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8975</v>
+        <v>-1.0446</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.378</v>
+        <v>-1.0334</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4805</v>
+        <v>-0.0112</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0218</v>
+        <v>-1.9242</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6373</v>
+        <v>-2.4723</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6156</v>
+        <v>0.5481</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6393</v>
+        <v>-1.1929</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1366</v>
+        <v>-1.9014</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7759</v>
+        <v>0.7085</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6611</v>
+        <v>-0.7312</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5008</v>
+        <v>-0.5709</v>
       </c>
       <c r="O21" t="n">
         <v>-0.1603</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1585</v>
+        <v>0.1465</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.101</v>
+        <v>0.1595</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0575</v>
+        <v>-0.013</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3875</v>
+        <v>-1.2666</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3024</v>
+        <v>-1.2062</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0851</v>
+        <v>-0.0603</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5837</v>
@@ -2170,13 +2170,13 @@
         <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1621</v>
+        <v>0.283</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2361</v>
+        <v>0.3322</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.074</v>
+        <v>-0.0492</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9658</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5064</v>
+        <v>-1.8589</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8303</v>
+        <v>1.3495</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3367</v>
+        <v>-3.2085</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8908</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8243</v>
+        <v>0.4717</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6765</v>
+        <v>0.1957</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1478</v>
+        <v>0.276</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6231</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7361</v>
+        <v>-2.455</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7298</v>
+        <v>-1.0567</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0063</v>
+        <v>-1.3983</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7782</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1313</v>
+        <v>0.4123</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.046</v>
+        <v>-0.3729</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1773</v>
+        <v>0.7852</v>
       </c>
       <c r="V24" t="n">
         <v>1.9109</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0814</v>
+        <v>-4.6196</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2306</v>
+        <v>-3.9421</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8509</v>
+        <v>-0.6774</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5704</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6551</v>
+        <v>-0.1932</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.405</v>
+        <v>-0.1165</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2502</v>
+        <v>-0.0767</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5889</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.2646</v>
+        <v>-8.6236</v>
       </c>
       <c r="E26" t="n">
-        <v>2.962699999999998</v>
+        <v>2.963</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.2275</v>
+        <v>-11.5862</v>
       </c>
       <c r="G26" t="n">
         <v>-11.2851</v>
@@ -2452,7 +2452,7 @@
         <v>-14.9735</v>
       </c>
       <c r="I26" t="n">
-        <v>3.688499999999999</v>
+        <v>3.688500000000001</v>
       </c>
       <c r="J26" t="n">
         <v>10.5747</v>
@@ -2482,13 +2482,13 @@
         <v>15.5768</v>
       </c>
       <c r="S26" t="n">
-        <v>2.285099999999999</v>
+        <v>2.9262</v>
       </c>
       <c r="T26" t="n">
         <v>0.8976999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3874</v>
+        <v>2.0287</v>
       </c>
       <c r="V26" t="n">
         <v>1.5681</v>
